--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 62 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 61 clubs short</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="X3" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2762,8 +2762,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6315,8 +6315,8 @@
       <c r="S55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T55" s="9" t="n">
-        <v>0</v>
+      <c r="T55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U55" s="9" t="n">
         <v>0</v>
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8158,8 +8158,8 @@
       <c r="T73" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U73" s="9" t="n">
-        <v>0</v>
+      <c r="U73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V73" s="9" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9293,8 +9293,8 @@
       <c r="T84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
+      <c r="U84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
         <v>0</v>
@@ -16297,7 +16297,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16528,7 +16528,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16627,7 +16627,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16693,7 +16693,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3385,7 +3389,11 @@
       <c r="AB26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4199,7 +4207,11 @@
       <c r="AB34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4300,7 +4312,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4918,7 +4934,11 @@
       <c r="AB41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -5419,7 +5439,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -9416,7 +9440,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -10951,7 +10979,11 @@
       <c r="AB100" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC100" s="4" t="inlineStr"/>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -12284,7 +12316,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12902,7 +12938,11 @@
       <c r="AB119" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 61 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1536,8 +1536,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2661,8 +2661,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4093,8 +4093,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5535,8 +5535,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7791,8 +7791,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10150,8 +10150,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -13289,13 +13289,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14359,8 +14359,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -16271,7 +16271,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16337,7 +16337,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16403,7 +16403,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16502,7 +16502,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16634,7 +16634,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16766,7 +16766,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17030,7 +17030,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 34 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1270,17 +1270,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1375,17 +1375,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2344,11 +2344,11 @@
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>3</v>
+      <c r="V16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>7</v>
@@ -2811,13 +2811,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5174,13 +5174,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="10" t="n">
         <v>1</v>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -8963,13 +8963,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9987,13 +9987,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11722,13 +11722,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12170,8 +12170,8 @@
       <c r="S112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
@@ -13170,13 +13170,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>4</v>
       </c>
       <c r="W122" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>5</v>
@@ -13275,13 +13275,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -14303,13 +14303,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14699,13 +14699,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>0</v>
       </c>
       <c r="S137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" s="10" t="n">
         <v>1</v>
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14897,13 +14897,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14996,13 +14996,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -16601,7 +16601,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -17195,7 +17195,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>

--- a/docs/d/83/inyear.xlsx
+++ b/docs/d/83/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 34 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2138,8 +2138,8 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>3</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="10" t="n">
         <v>2</v>
@@ -2347,8 +2347,8 @@
       <c r="V16" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>2</v>
+      <c r="W16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>7</v>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" s="9" t="n">
         <v>0</v>
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3855,8 +3855,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P31" s="9" t="n">
-        <v>3</v>
+      <c r="P31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4968,13 +4968,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5073,13 +5073,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -6093,13 +6093,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7426,13 +7426,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7729,13 +7729,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -9064,13 +9064,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9169,13 +9169,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -10092,13 +10092,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10603,13 +10603,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10734,7 +10734,7 @@
         <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9" t="n">
         <v>0</v>
@@ -10809,13 +10809,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -11011,13 +11011,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11722,13 +11722,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -13095,7 +13095,7 @@
         <v>1</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13170,13 +13170,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -13792,13 +13792,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" s="9" t="n">
         <v>0</v>
@@ -14702,10 +14702,10 @@
         <v>10</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>6</v>
@@ -15194,10 +15194,10 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K142" s="4" t="n">
         <v>-2</v>
@@ -15395,10 +15395,10 @@
         <v>7</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15491,13 +15491,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16184,13 +16184,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16228,8 +16228,8 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>3</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -16601,7 +16601,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16700,7 +16700,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -17177,7 +17177,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -17426,7 +17426,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
